--- a/03_Outputs/all/01_TablasDescriptivas/idx6_crecimiento_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx6_crecimiento_vr.xlsx
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.210756087931079</v>
+        <v>1.210756087931075</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.006134217277292</v>
+        <v>1.006134217277294</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.919245371472592</v>
+        <v>0.9192453714725922</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7579173073172567</v>
+        <v>0.7579173073172566</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.5687935708808259</v>
+        <v>0.5687935708808264</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.3312215018646288</v>
+        <v>0.3312215018646285</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>5.413121296855191E-30</v>
+        <v>5.035357335579454E-30</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>5.416688031187411</v>
+        <v>5.416688031187407</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>6.422822248464703</v>
+        <v>6.422822248464701</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>7.342067619937295</v>
+        <v>7.342067619937294</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>8.099984927254551</v>
+        <v>8.09998492725455</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>8.668778498135378</v>
+        <v>8.668778498135376</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>9.000000000000007</v>
+        <v>9.000000000000005</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>9.000000000000007</v>
+        <v>9.000000000000005</v>
       </c>
       <c r="C19">
         <v>9</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>27.96110343189929</v>
+        <v>27.9611034318993</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>18.77147371539325</v>
+        <v>18.77147371539326</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>13.45284542145642</v>
+        <v>13.45284542145638</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>11.17926908085879</v>
+        <v>11.17926908085881</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>6.319928565342506</v>
+        <v>6.319928565342511</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>3.680238909606984</v>
+        <v>3.680238909606981</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>6.014579218727985E-29</v>
+        <v>5.594841483977168E-29</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>27.96110343189929</v>
+        <v>27.9611034318993</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>60.18542256874896</v>
+        <v>60.18542256874893</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>71.36469164960776</v>
+        <v>71.36469164960775</v>
       </c>
       <c r="C32">
         <v>4</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>81.57852911041434</v>
+        <v>81.57852911041432</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>89.99983252505051</v>
+        <v>89.99983252505049</v>
       </c>
       <c r="C34">
         <v>6</v>
